--- a/research/traditional_assets/database/data/panama/panama_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/panama/panama_financial_svcs_non_bank_insurance.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.07480000000000001</v>
+        <v>0.0148</v>
       </c>
       <c r="E2">
-        <v>-0.0965</v>
+        <v>0.0164</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>58.4</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="L2">
-        <v>0.5971370143149284</v>
+        <v>0.6281951975213013</v>
       </c>
       <c r="M2">
-        <v>67.80000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="N2">
-        <v>0.1074314688638885</v>
+        <v>0.1152081563296516</v>
       </c>
       <c r="O2">
-        <v>1.160958904109589</v>
+        <v>0.8360049321824907</v>
       </c>
       <c r="P2">
-        <v>39.2</v>
+        <v>36.4</v>
       </c>
       <c r="Q2">
-        <v>0.06211376960861987</v>
+        <v>0.06185216652506372</v>
       </c>
       <c r="R2">
-        <v>0.6712328767123288</v>
+        <v>0.4488286066584464</v>
       </c>
       <c r="S2">
-        <v>28.60000000000001</v>
+        <v>31.4</v>
       </c>
       <c r="T2">
-        <v>0.4218289085545723</v>
+        <v>0.4631268436578171</v>
       </c>
       <c r="U2">
-        <v>632.3</v>
+        <v>953.7</v>
       </c>
       <c r="V2">
-        <v>1.001901441926794</v>
+        <v>1.620560747663552</v>
       </c>
       <c r="W2">
-        <v>0.05693672613824705</v>
+        <v>0.08008294657845363</v>
       </c>
       <c r="X2">
-        <v>0.05835025463218286</v>
+        <v>0.1402012707604583</v>
       </c>
       <c r="Y2">
-        <v>-0.001413528493935813</v>
+        <v>-0.06011832418200463</v>
       </c>
       <c r="Z2">
-        <v>0.05496543584555723</v>
+        <v>0.04788753292036056</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04031976902864619</v>
+        <v>0.07033160243832531</v>
       </c>
       <c r="AC2">
-        <v>-0.04031976902864619</v>
+        <v>-0.07033160243832531</v>
       </c>
       <c r="AD2">
-        <v>2315.5</v>
+        <v>4694.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2315.5</v>
+        <v>4694.4</v>
       </c>
       <c r="AG2">
-        <v>1683.2</v>
+        <v>3740.7</v>
       </c>
       <c r="AH2">
-        <v>0.7858209461752529</v>
+        <v>0.8886028507069981</v>
       </c>
       <c r="AI2">
-        <v>0.6957214109728983</v>
+        <v>0.8173698048160466</v>
       </c>
       <c r="AJ2">
-        <v>0.7273041524435034</v>
+        <v>0.8640626443684746</v>
       </c>
       <c r="AK2">
-        <v>0.624355502800549</v>
+        <v>0.7810046767997326</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Banco Latinoamericano de Comercio Exterior, S.A (NYSE:BLX)</t>
+          <t>Banco Latinoamericano de Comercio Exterior, S. A. (NYSE:BLX)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.07480000000000001</v>
+        <v>0.0148</v>
       </c>
       <c r="E3">
-        <v>-0.0965</v>
+        <v>0.0164</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +728,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>58.4</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="L3">
-        <v>0.5971370143149284</v>
+        <v>0.6281951975213013</v>
       </c>
       <c r="M3">
-        <v>67.80000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="N3">
-        <v>0.1074314688638885</v>
+        <v>0.1152081563296516</v>
       </c>
       <c r="O3">
-        <v>1.160958904109589</v>
+        <v>0.8360049321824907</v>
       </c>
       <c r="P3">
-        <v>39.2</v>
+        <v>36.4</v>
       </c>
       <c r="Q3">
-        <v>0.06211376960861987</v>
+        <v>0.06185216652506372</v>
       </c>
       <c r="R3">
-        <v>0.6712328767123288</v>
+        <v>0.4488286066584464</v>
       </c>
       <c r="S3">
-        <v>28.60000000000001</v>
+        <v>31.4</v>
       </c>
       <c r="T3">
-        <v>0.4218289085545723</v>
+        <v>0.4631268436578171</v>
       </c>
       <c r="U3">
-        <v>632.3</v>
+        <v>953.7</v>
       </c>
       <c r="V3">
-        <v>1.001901441926794</v>
+        <v>1.620560747663552</v>
       </c>
       <c r="W3">
-        <v>0.05693672613824705</v>
+        <v>0.08008294657845363</v>
       </c>
       <c r="X3">
-        <v>0.05835025463218286</v>
+        <v>0.1402012707604583</v>
       </c>
       <c r="Y3">
-        <v>-0.001413528493935813</v>
+        <v>-0.06011832418200463</v>
       </c>
       <c r="Z3">
-        <v>0.05496543584555723</v>
+        <v>0.04788753292036056</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04031976902864619</v>
+        <v>0.07033160243832531</v>
       </c>
       <c r="AC3">
-        <v>-0.04031976902864619</v>
+        <v>-0.07033160243832531</v>
       </c>
       <c r="AD3">
-        <v>2315.5</v>
+        <v>4694.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2315.5</v>
+        <v>4694.4</v>
       </c>
       <c r="AG3">
-        <v>1683.2</v>
+        <v>3740.7</v>
       </c>
       <c r="AH3">
-        <v>0.7858209461752529</v>
+        <v>0.8886028507069981</v>
       </c>
       <c r="AI3">
-        <v>0.6957214109728983</v>
+        <v>0.8173698048160466</v>
       </c>
       <c r="AJ3">
-        <v>0.7273041524435034</v>
+        <v>0.8640626443684746</v>
       </c>
       <c r="AK3">
-        <v>0.624355502800549</v>
+        <v>0.7810046767997326</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/panama/panama_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/panama/panama_financial_svcs_non_bank_insurance.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0148</v>
+        <v>0.266</v>
       </c>
       <c r="E2">
-        <v>0.0164</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>81.09999999999999</v>
+        <v>150.8</v>
       </c>
       <c r="L2">
-        <v>0.6281951975213013</v>
+        <v>0.6911090742438131</v>
       </c>
       <c r="M2">
-        <v>67.8</v>
+        <v>36.2</v>
       </c>
       <c r="N2">
-        <v>0.1152081563296516</v>
+        <v>0.04004424778761062</v>
       </c>
       <c r="O2">
-        <v>0.8360049321824907</v>
+        <v>0.240053050397878</v>
       </c>
       <c r="P2">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="Q2">
-        <v>0.06185216652506372</v>
+        <v>0.04004424778761062</v>
       </c>
       <c r="R2">
-        <v>0.4488286066584464</v>
+        <v>0.240053050397878</v>
       </c>
       <c r="S2">
-        <v>31.4</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.4631268436578171</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>953.7</v>
+        <v>1544.5</v>
       </c>
       <c r="V2">
-        <v>1.620560747663552</v>
+        <v>1.708517699115044</v>
       </c>
       <c r="W2">
-        <v>0.08008294657845363</v>
+        <v>0.1437696634569549</v>
       </c>
       <c r="X2">
-        <v>0.1402012707604583</v>
+        <v>0.1200903427456698</v>
       </c>
       <c r="Y2">
-        <v>-0.06011832418200463</v>
+        <v>0.02367932071128506</v>
       </c>
       <c r="Z2">
-        <v>0.04788753292036056</v>
+        <v>0.04555704025388341</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07033160243832531</v>
+        <v>0.0668118856395841</v>
       </c>
       <c r="AC2">
-        <v>-0.07033160243832531</v>
+        <v>-0.0668118856395841</v>
       </c>
       <c r="AD2">
-        <v>4694.4</v>
+        <v>4334.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4694.4</v>
+        <v>4334.6</v>
       </c>
       <c r="AG2">
-        <v>3740.7</v>
+        <v>2790.1</v>
       </c>
       <c r="AH2">
-        <v>0.8886028507069981</v>
+        <v>0.8274348108273203</v>
       </c>
       <c r="AI2">
-        <v>0.8173698048160466</v>
+        <v>0.7887400829754713</v>
       </c>
       <c r="AJ2">
-        <v>0.8640626443684746</v>
+        <v>0.7552854551852954</v>
       </c>
       <c r="AK2">
-        <v>0.7810046767997326</v>
+        <v>0.7061577788463972</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0148</v>
+        <v>0.266</v>
       </c>
       <c r="E3">
-        <v>0.0164</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +728,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>81.09999999999999</v>
+        <v>150.8</v>
       </c>
       <c r="L3">
-        <v>0.6281951975213013</v>
+        <v>0.6911090742438131</v>
       </c>
       <c r="M3">
-        <v>67.8</v>
+        <v>36.2</v>
       </c>
       <c r="N3">
-        <v>0.1152081563296516</v>
+        <v>0.04004424778761062</v>
       </c>
       <c r="O3">
-        <v>0.8360049321824907</v>
+        <v>0.240053050397878</v>
       </c>
       <c r="P3">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="Q3">
-        <v>0.06185216652506372</v>
+        <v>0.04004424778761062</v>
       </c>
       <c r="R3">
-        <v>0.4488286066584464</v>
+        <v>0.240053050397878</v>
       </c>
       <c r="S3">
-        <v>31.4</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.4631268436578171</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>953.7</v>
+        <v>1544.5</v>
       </c>
       <c r="V3">
-        <v>1.620560747663552</v>
+        <v>1.708517699115044</v>
       </c>
       <c r="W3">
-        <v>0.08008294657845363</v>
+        <v>0.1437696634569549</v>
       </c>
       <c r="X3">
-        <v>0.1402012707604583</v>
+        <v>0.1200903427456698</v>
       </c>
       <c r="Y3">
-        <v>-0.06011832418200463</v>
+        <v>0.02367932071128506</v>
       </c>
       <c r="Z3">
-        <v>0.04788753292036056</v>
+        <v>0.04555704025388341</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07033160243832531</v>
+        <v>0.0668118856395841</v>
       </c>
       <c r="AC3">
-        <v>-0.07033160243832531</v>
+        <v>-0.0668118856395841</v>
       </c>
       <c r="AD3">
-        <v>4694.4</v>
+        <v>4334.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4694.4</v>
+        <v>4334.6</v>
       </c>
       <c r="AG3">
-        <v>3740.7</v>
+        <v>2790.1</v>
       </c>
       <c r="AH3">
-        <v>0.8886028507069981</v>
+        <v>0.8274348108273203</v>
       </c>
       <c r="AI3">
-        <v>0.8173698048160466</v>
+        <v>0.7887400829754713</v>
       </c>
       <c r="AJ3">
-        <v>0.8640626443684746</v>
+        <v>0.7552854551852954</v>
       </c>
       <c r="AK3">
-        <v>0.7810046767997326</v>
+        <v>0.7061577788463972</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/panama/panama_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/panama/panama_financial_svcs_non_bank_insurance.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.266</v>
+        <v>0.169</v>
       </c>
       <c r="E2">
-        <v>0.6879999999999999</v>
+        <v>0.188</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>150.8</v>
+        <v>200.8</v>
       </c>
       <c r="L2">
-        <v>0.6911090742438131</v>
+        <v>0.7176554681915654</v>
       </c>
       <c r="M2">
-        <v>36.2</v>
+        <v>63.6</v>
       </c>
       <c r="N2">
-        <v>0.04004424778761062</v>
+        <v>0.04860527321360336</v>
       </c>
       <c r="O2">
-        <v>0.240053050397878</v>
+        <v>0.3167330677290837</v>
       </c>
       <c r="P2">
-        <v>36.2</v>
+        <v>63.6</v>
       </c>
       <c r="Q2">
-        <v>0.04004424778761062</v>
+        <v>0.04860527321360336</v>
       </c>
       <c r="R2">
-        <v>0.240053050397878</v>
+        <v>0.3167330677290837</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1544.5</v>
+        <v>1608.4</v>
       </c>
       <c r="V2">
-        <v>1.708517699115044</v>
+        <v>1.229193733282385</v>
       </c>
       <c r="W2">
-        <v>0.1437696634569549</v>
+        <v>0.1729543496985358</v>
       </c>
       <c r="X2">
-        <v>0.1200903427456698</v>
+        <v>0.1033436981265463</v>
       </c>
       <c r="Y2">
-        <v>0.02367932071128506</v>
+        <v>0.06961065157198948</v>
       </c>
       <c r="Z2">
-        <v>0.04555704025388341</v>
+        <v>0.07081572220394321</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0668118856395841</v>
+        <v>0.07039023781891969</v>
       </c>
       <c r="AC2">
-        <v>-0.0668118856395841</v>
+        <v>-0.07039023781891969</v>
       </c>
       <c r="AD2">
-        <v>4334.6</v>
+        <v>4024.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4334.6</v>
+        <v>4024.4</v>
       </c>
       <c r="AG2">
-        <v>2790.1</v>
+        <v>2416</v>
       </c>
       <c r="AH2">
-        <v>0.8274348108273203</v>
+        <v>0.7546363142005289</v>
       </c>
       <c r="AI2">
-        <v>0.7887400829754713</v>
+        <v>0.7544524014847588</v>
       </c>
       <c r="AJ2">
-        <v>0.7552854551852954</v>
+        <v>0.6486776748556853</v>
       </c>
       <c r="AK2">
-        <v>0.7061577788463972</v>
+        <v>0.6484513393096785</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.266</v>
+        <v>0.169</v>
       </c>
       <c r="E3">
-        <v>0.6879999999999999</v>
+        <v>0.188</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>150.8</v>
+        <v>200.8</v>
       </c>
       <c r="L3">
-        <v>0.6911090742438131</v>
+        <v>0.7176554681915654</v>
       </c>
       <c r="M3">
-        <v>36.2</v>
+        <v>63.6</v>
       </c>
       <c r="N3">
-        <v>0.04004424778761062</v>
+        <v>0.04860527321360336</v>
       </c>
       <c r="O3">
-        <v>0.240053050397878</v>
+        <v>0.3167330677290837</v>
       </c>
       <c r="P3">
-        <v>36.2</v>
+        <v>63.6</v>
       </c>
       <c r="Q3">
-        <v>0.04004424778761062</v>
+        <v>0.04860527321360336</v>
       </c>
       <c r="R3">
-        <v>0.240053050397878</v>
+        <v>0.3167330677290837</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,55 +758,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1544.5</v>
+        <v>1608.4</v>
       </c>
       <c r="V3">
-        <v>1.708517699115044</v>
+        <v>1.229193733282385</v>
       </c>
       <c r="W3">
-        <v>0.1437696634569549</v>
+        <v>0.1729543496985358</v>
       </c>
       <c r="X3">
-        <v>0.1200903427456698</v>
+        <v>0.1033436981265463</v>
       </c>
       <c r="Y3">
-        <v>0.02367932071128506</v>
+        <v>0.06961065157198948</v>
       </c>
       <c r="Z3">
-        <v>0.04555704025388341</v>
+        <v>0.07081572220394321</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0668118856395841</v>
+        <v>0.07039023781891969</v>
       </c>
       <c r="AC3">
-        <v>-0.0668118856395841</v>
+        <v>-0.07039023781891969</v>
       </c>
       <c r="AD3">
-        <v>4334.6</v>
+        <v>4024.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4334.6</v>
+        <v>4024.4</v>
       </c>
       <c r="AG3">
-        <v>2790.1</v>
+        <v>2416</v>
       </c>
       <c r="AH3">
-        <v>0.8274348108273203</v>
+        <v>0.7546363142005289</v>
       </c>
       <c r="AI3">
-        <v>0.7887400829754713</v>
+        <v>0.7544524014847588</v>
       </c>
       <c r="AJ3">
-        <v>0.7552854551852954</v>
+        <v>0.6486776748556853</v>
       </c>
       <c r="AK3">
-        <v>0.7061577788463972</v>
+        <v>0.6484513393096785</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/panama/panama_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/panama/panama_financial_svcs_non_bank_insurance.xlsx
@@ -645,10 +645,10 @@
         <v>0.1729543496985358</v>
       </c>
       <c r="X2">
-        <v>0.1033436981265463</v>
+        <v>0.1033329203318308</v>
       </c>
       <c r="Y2">
-        <v>0.06961065157198948</v>
+        <v>0.06962142936670501</v>
       </c>
       <c r="Z2">
         <v>0.07081572220394321</v>
@@ -657,10 +657,10 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07039023781891969</v>
+        <v>0.0703875933394835</v>
       </c>
       <c r="AC2">
-        <v>-0.07039023781891969</v>
+        <v>-0.0703875933394835</v>
       </c>
       <c r="AD2">
         <v>4024.4</v>
@@ -767,10 +767,10 @@
         <v>0.1729543496985358</v>
       </c>
       <c r="X3">
-        <v>0.1033436981265463</v>
+        <v>0.1033329203318308</v>
       </c>
       <c r="Y3">
-        <v>0.06961065157198948</v>
+        <v>0.06962142936670501</v>
       </c>
       <c r="Z3">
         <v>0.07081572220394321</v>
@@ -779,10 +779,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07039023781891969</v>
+        <v>0.0703875933394835</v>
       </c>
       <c r="AC3">
-        <v>-0.07039023781891969</v>
+        <v>-0.0703875933394835</v>
       </c>
       <c r="AD3">
         <v>4024.4</v>
